--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$21</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="154">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:42:19+00:00</t>
+    <t>2026-07-09T18:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -264,6 +267,9 @@
   </si>
   <si>
     <t>pdlgc-contact-portabilite.nom</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -612,6 +618,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -935,7 +956,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>71</v>
       </c>
@@ -1035,7 +1056,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>77</v>
       </c>
@@ -1154,7 +1175,7 @@
         <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>72</v>
@@ -1163,13 +1184,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1220,7 +1241,7 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
@@ -1235,12 +1256,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1263,13 +1284,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1320,7 +1341,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1335,12 +1356,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1363,13 +1384,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1396,11 +1417,11 @@
         <v>72</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>72</v>
@@ -1418,7 +1439,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1433,12 +1454,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1461,13 +1482,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1494,11 +1515,11 @@
         <v>72</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y7" s="2"/>
       <c r="Z7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>72</v>
@@ -1516,7 +1537,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1531,12 +1552,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1559,13 +1580,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1616,7 +1637,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1631,12 +1652,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1659,13 +1680,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1692,11 +1713,11 @@
         <v>72</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>72</v>
@@ -1714,7 +1735,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1729,12 +1750,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1757,13 +1778,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1814,7 +1835,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1829,12 +1850,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1857,13 +1878,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1890,11 +1911,11 @@
         <v>72</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>72</v>
@@ -1912,7 +1933,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1927,12 +1948,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1955,13 +1976,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1988,11 +2009,11 @@
         <v>72</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>72</v>
@@ -2010,7 +2031,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -2025,12 +2046,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2053,13 +2074,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2110,7 +2131,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2125,12 +2146,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2153,13 +2174,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2210,7 +2231,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2225,12 +2246,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2253,13 +2274,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2286,11 +2307,11 @@
         <v>72</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>72</v>
@@ -2308,7 +2329,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2323,12 +2344,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2351,13 +2372,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2408,7 +2429,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2423,12 +2444,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2451,13 +2472,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2508,7 +2529,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2525,10 +2546,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2542,7 +2563,7 @@
         <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>72</v>
@@ -2551,13 +2572,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2608,7 +2629,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2623,12 +2644,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2651,13 +2672,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2708,7 +2729,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2723,12 +2744,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2751,13 +2772,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2808,7 +2829,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2823,12 +2844,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2851,13 +2872,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2908,7 +2929,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2924,6 +2945,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ21">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI20">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-contact-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
